--- a/data/nzd0006/nzd0006.xlsx
+++ b/data/nzd0006/nzd0006.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P208"/>
+  <dimension ref="A1:P209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11686,6 +11686,60 @@
         <v>351.53</v>
       </c>
       <c r="P208" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>347.68</v>
+      </c>
+      <c r="C209" t="n">
+        <v>330.24</v>
+      </c>
+      <c r="D209" t="n">
+        <v>322.01</v>
+      </c>
+      <c r="E209" t="n">
+        <v>318.24</v>
+      </c>
+      <c r="F209" t="n">
+        <v>309.79</v>
+      </c>
+      <c r="G209" t="n">
+        <v>313.08</v>
+      </c>
+      <c r="H209" t="n">
+        <v>316.82</v>
+      </c>
+      <c r="I209" t="n">
+        <v>321</v>
+      </c>
+      <c r="J209" t="n">
+        <v>326.26</v>
+      </c>
+      <c r="K209" t="n">
+        <v>334.32</v>
+      </c>
+      <c r="L209" t="n">
+        <v>348.1</v>
+      </c>
+      <c r="M209" t="n">
+        <v>353.39</v>
+      </c>
+      <c r="N209" t="n">
+        <v>355.59</v>
+      </c>
+      <c r="O209" t="n">
+        <v>355.57</v>
+      </c>
+      <c r="P209" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11702,7 +11756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B211"/>
+  <dimension ref="A1:B212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13815,6 +13869,16 @@
       </c>
       <c r="B211" t="n">
         <v>-0.23</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
@@ -13983,28 +14047,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2677374951479313</v>
+        <v>-0.2752218218390552</v>
       </c>
       <c r="J2" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K2" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06360170527428233</v>
+        <v>0.06737753908293032</v>
       </c>
       <c r="M2" t="n">
-        <v>6.307614976554171</v>
+        <v>6.319271866484322</v>
       </c>
       <c r="N2" t="n">
-        <v>62.4789066453217</v>
+        <v>62.47253200182338</v>
       </c>
       <c r="O2" t="n">
-        <v>7.904359976957129</v>
+        <v>7.903956730766141</v>
       </c>
       <c r="P2" t="n">
-        <v>362.5215809375217</v>
+        <v>362.5901995452137</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14061,28 +14125,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3556522040101773</v>
+        <v>-0.3687976867548382</v>
       </c>
       <c r="J3" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K3" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0558457264073754</v>
+        <v>0.06003067701790576</v>
       </c>
       <c r="M3" t="n">
-        <v>8.83803531144016</v>
+        <v>8.8629012792785</v>
       </c>
       <c r="N3" t="n">
-        <v>126.5981043214102</v>
+        <v>126.8964483434214</v>
       </c>
       <c r="O3" t="n">
-        <v>11.25158230301011</v>
+        <v>11.26483237085317</v>
       </c>
       <c r="P3" t="n">
-        <v>353.3326623450737</v>
+        <v>353.4531841716326</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14139,28 +14203,28 @@
         <v>0.1034</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2945805929365005</v>
+        <v>-0.3051701265184537</v>
       </c>
       <c r="J4" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K4" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03037454442996324</v>
+        <v>0.0327680960375506</v>
       </c>
       <c r="M4" t="n">
-        <v>10.46968450486365</v>
+        <v>10.46188199293655</v>
       </c>
       <c r="N4" t="n">
-        <v>163.9931373568687</v>
+        <v>163.7932847280873</v>
       </c>
       <c r="O4" t="n">
-        <v>12.80598053086403</v>
+        <v>12.79817505459616</v>
       </c>
       <c r="P4" t="n">
-        <v>340.8201921267584</v>
+        <v>340.9172802257272</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14217,28 +14281,28 @@
         <v>0.0706</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3986923435054167</v>
+        <v>-0.4092931037788172</v>
       </c>
       <c r="J5" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K5" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05020781969631594</v>
+        <v>0.05317001558199563</v>
       </c>
       <c r="M5" t="n">
-        <v>10.57489111455822</v>
+        <v>10.56760793967521</v>
       </c>
       <c r="N5" t="n">
-        <v>178.01483389322</v>
+        <v>177.7488179028551</v>
       </c>
       <c r="O5" t="n">
-        <v>13.34221997619662</v>
+        <v>13.33224729379316</v>
       </c>
       <c r="P5" t="n">
-        <v>339.7712802413424</v>
+        <v>339.8684712700691</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14295,28 +14359,28 @@
         <v>0.0582</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5033944369147513</v>
+        <v>-0.5188962425395336</v>
       </c>
       <c r="J6" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K6" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07559931884765203</v>
+        <v>0.08027359139992518</v>
       </c>
       <c r="M6" t="n">
-        <v>10.2529806727232</v>
+        <v>10.28531036361899</v>
       </c>
       <c r="N6" t="n">
-        <v>183.4350712644737</v>
+        <v>183.8144573673357</v>
       </c>
       <c r="O6" t="n">
-        <v>13.54382040875002</v>
+        <v>13.55781904907038</v>
       </c>
       <c r="P6" t="n">
-        <v>339.2056828878084</v>
+        <v>339.3478082068364</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14373,28 +14437,28 @@
         <v>0.0497</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3267255669423101</v>
+        <v>-0.3393295365779539</v>
       </c>
       <c r="J7" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K7" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03405579555696558</v>
+        <v>0.03687041467862795</v>
       </c>
       <c r="M7" t="n">
-        <v>9.928548878000043</v>
+        <v>9.946223762358937</v>
       </c>
       <c r="N7" t="n">
-        <v>179.2463935716629</v>
+        <v>179.2184351918829</v>
       </c>
       <c r="O7" t="n">
-        <v>13.38829315378413</v>
+        <v>13.3872489777356</v>
       </c>
       <c r="P7" t="n">
-        <v>334.8502313593264</v>
+        <v>334.9657884272474</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14451,28 +14515,28 @@
         <v>0.051</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3904847151389709</v>
+        <v>-0.3962466105743392</v>
       </c>
       <c r="J8" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K8" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03900513781955928</v>
+        <v>0.04052456246374347</v>
       </c>
       <c r="M8" t="n">
-        <v>11.49781385251129</v>
+        <v>11.47184005175006</v>
       </c>
       <c r="N8" t="n">
-        <v>222.3978075551208</v>
+        <v>221.5028400475803</v>
       </c>
       <c r="O8" t="n">
-        <v>14.91300799822493</v>
+        <v>14.88297147909584</v>
       </c>
       <c r="P8" t="n">
-        <v>333.0435965867946</v>
+        <v>333.0964234152802</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14529,28 +14593,28 @@
         <v>0.0674</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2906178543296983</v>
+        <v>-0.2929865311915049</v>
       </c>
       <c r="J9" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K9" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02421307361317271</v>
+        <v>0.02486838520359969</v>
       </c>
       <c r="M9" t="n">
-        <v>11.06409200224651</v>
+        <v>11.02189786973482</v>
       </c>
       <c r="N9" t="n">
-        <v>201.4989705207768</v>
+        <v>200.5596737857979</v>
       </c>
       <c r="O9" t="n">
-        <v>14.19503330467304</v>
+        <v>14.16190925637493</v>
       </c>
       <c r="P9" t="n">
-        <v>331.0506036142508</v>
+        <v>331.0723203718213</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -14607,28 +14671,28 @@
         <v>0.0619</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.366826774720301</v>
+        <v>-0.368918106799236</v>
       </c>
       <c r="J10" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K10" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04343062543619247</v>
+        <v>0.0443761726571158</v>
       </c>
       <c r="M10" t="n">
-        <v>10.19164873665042</v>
+        <v>10.15113199574896</v>
       </c>
       <c r="N10" t="n">
-        <v>175.4549472597313</v>
+        <v>174.6343697857425</v>
       </c>
       <c r="O10" t="n">
-        <v>13.24594078424524</v>
+        <v>13.21492980631159</v>
       </c>
       <c r="P10" t="n">
-        <v>338.0023028014218</v>
+        <v>338.0214767767706</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -14685,28 +14749,28 @@
         <v>0.0475</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2332942099140123</v>
+        <v>-0.2360382293285127</v>
       </c>
       <c r="J11" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K11" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01906480501033314</v>
+        <v>0.01971957740846242</v>
       </c>
       <c r="M11" t="n">
-        <v>10.16997608069108</v>
+        <v>10.13750456115665</v>
       </c>
       <c r="N11" t="n">
-        <v>165.7826374123564</v>
+        <v>165.0251260701958</v>
       </c>
       <c r="O11" t="n">
-        <v>12.8756606592577</v>
+        <v>12.84621057239043</v>
       </c>
       <c r="P11" t="n">
-        <v>343.2731172103221</v>
+        <v>343.2982752237913</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -14763,28 +14827,28 @@
         <v>0.0616</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3957762801760449</v>
+        <v>-0.3894467030152936</v>
       </c>
       <c r="J12" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K12" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05011389040393233</v>
+        <v>0.0490696033162733</v>
       </c>
       <c r="M12" t="n">
-        <v>11.03095846535417</v>
+        <v>11.0044393302467</v>
       </c>
       <c r="N12" t="n">
-        <v>175.766505189909</v>
+        <v>175.1317540370242</v>
       </c>
       <c r="O12" t="n">
-        <v>13.25769607397564</v>
+        <v>13.23373545288798</v>
       </c>
       <c r="P12" t="n">
-        <v>351.7186714254017</v>
+        <v>351.6606399163596</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -14841,28 +14905,28 @@
         <v>0.0581</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2713008826563895</v>
+        <v>-0.2659821542813449</v>
       </c>
       <c r="J13" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K13" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02382311413083549</v>
+        <v>0.02315464517404087</v>
       </c>
       <c r="M13" t="n">
-        <v>10.47104587253843</v>
+        <v>10.44153710789104</v>
       </c>
       <c r="N13" t="n">
-        <v>178.5482414367859</v>
+        <v>177.8383152291443</v>
       </c>
       <c r="O13" t="n">
-        <v>13.36219448431978</v>
+        <v>13.33560329453243</v>
       </c>
       <c r="P13" t="n">
-        <v>354.8432127371469</v>
+        <v>354.7944490004944</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -14919,28 +14983,28 @@
         <v>0.0492</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4230679491269125</v>
+        <v>-0.4166430127960698</v>
       </c>
       <c r="J14" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K14" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04904346662560166</v>
+        <v>0.04810181506320421</v>
       </c>
       <c r="M14" t="n">
-        <v>11.42401075996624</v>
+        <v>11.39634981551143</v>
       </c>
       <c r="N14" t="n">
-        <v>205.4579408627231</v>
+        <v>204.6868261628493</v>
       </c>
       <c r="O14" t="n">
-        <v>14.33380413089013</v>
+        <v>14.30688037843503</v>
       </c>
       <c r="P14" t="n">
-        <v>359.8257752455586</v>
+        <v>359.766869454333</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -14997,28 +15061,28 @@
         <v>0.0406</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6950680395872765</v>
+        <v>-0.688064373811909</v>
       </c>
       <c r="J15" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K15" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1047359666819465</v>
+        <v>0.1037997743237005</v>
       </c>
       <c r="M15" t="n">
-        <v>12.7351098891941</v>
+        <v>12.70322345496766</v>
       </c>
       <c r="N15" t="n">
-        <v>244.474240439246</v>
+        <v>243.5563375171676</v>
       </c>
       <c r="O15" t="n">
-        <v>15.63567204949138</v>
+        <v>15.60629160041448</v>
       </c>
       <c r="P15" t="n">
-        <v>366.2598271076116</v>
+        <v>366.1956153469443</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -15056,7 +15120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P208"/>
+  <dimension ref="A1:P209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32115,6 +32179,88 @@
         </is>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>-34.454913157859615,173.00343346551216</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>-34.455650254284784,173.00322391587363</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>-34.45638916439742,173.00311460987268</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>-34.45712894950098,173.00305384794453</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-34.45786780286076,173.0029421445658</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-34.45860897042676,173.00295822790147</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-34.459342810715725,173.00297949016863</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-34.46007015428859,173.00297540489507</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>-34.460805660340014,173.00295321969895</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>-34.46154984888759,173.00296075253837</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>-34.46230111638772,173.00303005657153</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>-34.46304707751864,173.00303730612526</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>-34.46378968399507,173.00304078721015</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>-34.46453013231506,173.00302017346823</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0006/nzd0006.xlsx
+++ b/data/nzd0006/nzd0006.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P209"/>
+  <dimension ref="A1:P211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11740,6 +11740,114 @@
         <v>355.57</v>
       </c>
       <c r="P209" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>347.5</v>
+      </c>
+      <c r="C210" t="n">
+        <v>327.75</v>
+      </c>
+      <c r="D210" t="n">
+        <v>320.65</v>
+      </c>
+      <c r="E210" t="n">
+        <v>316.83</v>
+      </c>
+      <c r="F210" t="n">
+        <v>307.17</v>
+      </c>
+      <c r="G210" t="n">
+        <v>309.78</v>
+      </c>
+      <c r="H210" t="n">
+        <v>313.87</v>
+      </c>
+      <c r="I210" t="n">
+        <v>318.74</v>
+      </c>
+      <c r="J210" t="n">
+        <v>325.01</v>
+      </c>
+      <c r="K210" t="n">
+        <v>332.28</v>
+      </c>
+      <c r="L210" t="n">
+        <v>343.16</v>
+      </c>
+      <c r="M210" t="n">
+        <v>350.67</v>
+      </c>
+      <c r="N210" t="n">
+        <v>354.01</v>
+      </c>
+      <c r="O210" t="n">
+        <v>351.25</v>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>347.5</v>
+      </c>
+      <c r="C211" t="n">
+        <v>327.75</v>
+      </c>
+      <c r="D211" t="n">
+        <v>320.65</v>
+      </c>
+      <c r="E211" t="n">
+        <v>316.51</v>
+      </c>
+      <c r="F211" t="n">
+        <v>309.65</v>
+      </c>
+      <c r="G211" t="n">
+        <v>311.17</v>
+      </c>
+      <c r="H211" t="n">
+        <v>315.3</v>
+      </c>
+      <c r="I211" t="n">
+        <v>319.81</v>
+      </c>
+      <c r="J211" t="n">
+        <v>327.89</v>
+      </c>
+      <c r="K211" t="n">
+        <v>333.16</v>
+      </c>
+      <c r="L211" t="n">
+        <v>345.29</v>
+      </c>
+      <c r="M211" t="n">
+        <v>353.8</v>
+      </c>
+      <c r="N211" t="n">
+        <v>357.04</v>
+      </c>
+      <c r="O211" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="P211" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11756,7 +11864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B212"/>
+  <dimension ref="A1:B214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13879,6 +13987,26 @@
       </c>
       <c r="B212" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -14047,28 +14175,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2752218218390552</v>
+        <v>-0.289877356574199</v>
       </c>
       <c r="J2" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K2" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06737753908293032</v>
+        <v>0.07508671836656888</v>
       </c>
       <c r="M2" t="n">
-        <v>6.319271866484322</v>
+        <v>6.343001951611255</v>
       </c>
       <c r="N2" t="n">
-        <v>62.47253200182338</v>
+        <v>62.455659531906</v>
       </c>
       <c r="O2" t="n">
-        <v>7.903956730766141</v>
+        <v>7.902889315427998</v>
       </c>
       <c r="P2" t="n">
-        <v>362.5901995452137</v>
+        <v>362.725046358222</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14125,28 +14253,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3687976867548382</v>
+        <v>-0.3985776508732214</v>
       </c>
       <c r="J3" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K3" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06003067701790576</v>
+        <v>0.06963394986266458</v>
       </c>
       <c r="M3" t="n">
-        <v>8.8629012792785</v>
+        <v>8.933471237732057</v>
       </c>
       <c r="N3" t="n">
-        <v>126.8964483434214</v>
+        <v>128.0749021228672</v>
       </c>
       <c r="O3" t="n">
-        <v>11.26483237085317</v>
+        <v>11.31701825229893</v>
       </c>
       <c r="P3" t="n">
-        <v>353.4531841716326</v>
+        <v>353.7271921554574</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14203,28 +14331,28 @@
         <v>0.1034</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3051701265184537</v>
+        <v>-0.327961245358953</v>
       </c>
       <c r="J4" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K4" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0327680960375506</v>
+        <v>0.03814969968280613</v>
       </c>
       <c r="M4" t="n">
-        <v>10.46188199293655</v>
+        <v>10.4526619732139</v>
       </c>
       <c r="N4" t="n">
-        <v>163.7932847280873</v>
+        <v>163.6314344805654</v>
       </c>
       <c r="O4" t="n">
-        <v>12.79817505459616</v>
+        <v>12.79185031496872</v>
       </c>
       <c r="P4" t="n">
-        <v>340.9172802257272</v>
+        <v>341.1269832472384</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14281,28 +14409,28 @@
         <v>0.0706</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4092931037788172</v>
+        <v>-0.4324914837755658</v>
       </c>
       <c r="J5" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K5" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05317001558199563</v>
+        <v>0.05978313827483683</v>
       </c>
       <c r="M5" t="n">
-        <v>10.56760793967521</v>
+        <v>10.56917556247147</v>
       </c>
       <c r="N5" t="n">
-        <v>177.7488179028551</v>
+        <v>177.5046640919324</v>
       </c>
       <c r="O5" t="n">
-        <v>13.33224729379316</v>
+        <v>13.3230876335755</v>
       </c>
       <c r="P5" t="n">
-        <v>339.8684712700691</v>
+        <v>340.0819229461576</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14359,28 +14487,28 @@
         <v>0.0582</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5188962425395336</v>
+        <v>-0.5511215407447333</v>
       </c>
       <c r="J6" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K6" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08027359139992518</v>
+        <v>0.09019308027286765</v>
       </c>
       <c r="M6" t="n">
-        <v>10.28531036361899</v>
+        <v>10.36534829614521</v>
       </c>
       <c r="N6" t="n">
-        <v>183.8144573673357</v>
+        <v>184.8741161299059</v>
       </c>
       <c r="O6" t="n">
-        <v>13.55781904907038</v>
+        <v>13.59684213815494</v>
       </c>
       <c r="P6" t="n">
-        <v>339.3478082068364</v>
+        <v>339.6443048731585</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14437,28 +14565,28 @@
         <v>0.0497</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3393295365779539</v>
+        <v>-0.3682921047353204</v>
       </c>
       <c r="J7" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K7" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03687041467862795</v>
+        <v>0.0435439410929066</v>
       </c>
       <c r="M7" t="n">
-        <v>9.946223762358937</v>
+        <v>10.00852365456021</v>
       </c>
       <c r="N7" t="n">
-        <v>179.2184351918829</v>
+        <v>179.774226522008</v>
       </c>
       <c r="O7" t="n">
-        <v>13.3872489777356</v>
+        <v>13.40799114416503</v>
       </c>
       <c r="P7" t="n">
-        <v>334.9657884272474</v>
+        <v>335.2322692783973</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14515,28 +14643,28 @@
         <v>0.051</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3962466105743392</v>
+        <v>-0.4113924030220823</v>
       </c>
       <c r="J8" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K8" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04052456246374347</v>
+        <v>0.04435676096373908</v>
       </c>
       <c r="M8" t="n">
-        <v>11.47184005175006</v>
+        <v>11.44202229958013</v>
       </c>
       <c r="N8" t="n">
-        <v>221.5028400475803</v>
+        <v>220.015776597867</v>
       </c>
       <c r="O8" t="n">
-        <v>14.88297147909584</v>
+        <v>14.83292879366267</v>
       </c>
       <c r="P8" t="n">
-        <v>333.0964234152802</v>
+        <v>333.2357747448352</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14593,28 +14721,28 @@
         <v>0.0674</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2929865311915049</v>
+        <v>-0.3006915416257423</v>
       </c>
       <c r="J9" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K9" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02486838520359969</v>
+        <v>0.02670839376945777</v>
       </c>
       <c r="M9" t="n">
-        <v>11.02189786973482</v>
+        <v>10.95214434734002</v>
       </c>
       <c r="N9" t="n">
-        <v>200.5596737857979</v>
+        <v>198.8121643793173</v>
       </c>
       <c r="O9" t="n">
-        <v>14.16190925637493</v>
+        <v>14.10007675083073</v>
       </c>
       <c r="P9" t="n">
-        <v>331.0723203718213</v>
+        <v>331.1432100567121</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -14671,28 +14799,28 @@
         <v>0.0619</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.368918106799236</v>
+        <v>-0.3725280866148421</v>
       </c>
       <c r="J10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0443761726571158</v>
+        <v>0.04616214083304782</v>
       </c>
       <c r="M10" t="n">
-        <v>10.15113199574896</v>
+        <v>10.0688632761558</v>
       </c>
       <c r="N10" t="n">
-        <v>174.6343697857425</v>
+        <v>173.0262441143227</v>
       </c>
       <c r="O10" t="n">
-        <v>13.21492980631159</v>
+        <v>13.15394405166461</v>
       </c>
       <c r="P10" t="n">
-        <v>338.0214767767706</v>
+        <v>338.0546796492187</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -14749,28 +14877,28 @@
         <v>0.0475</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2360382293285127</v>
+        <v>-0.2442304587907252</v>
       </c>
       <c r="J11" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K11" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01971957740846242</v>
+        <v>0.02152173850113215</v>
       </c>
       <c r="M11" t="n">
-        <v>10.13750456115665</v>
+        <v>10.08925223847102</v>
       </c>
       <c r="N11" t="n">
-        <v>165.0251260701958</v>
+        <v>163.6359809896162</v>
       </c>
       <c r="O11" t="n">
-        <v>12.84621057239043</v>
+        <v>12.79202802489176</v>
       </c>
       <c r="P11" t="n">
-        <v>343.2982752237913</v>
+        <v>343.3736487136125</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -14827,28 +14955,28 @@
         <v>0.0616</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3894467030152936</v>
+        <v>-0.3844114535755563</v>
       </c>
       <c r="J12" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K12" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0490696033162733</v>
+        <v>0.04886879691778612</v>
       </c>
       <c r="M12" t="n">
-        <v>11.0044393302467</v>
+        <v>10.92035383182295</v>
       </c>
       <c r="N12" t="n">
-        <v>175.1317540370242</v>
+        <v>173.5428568997539</v>
       </c>
       <c r="O12" t="n">
-        <v>13.23373545288798</v>
+        <v>13.17356659753743</v>
       </c>
       <c r="P12" t="n">
-        <v>351.6606399163596</v>
+        <v>351.6143006681094</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -14905,28 +15033,28 @@
         <v>0.0581</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2659821542813449</v>
+        <v>-0.2578738968018114</v>
       </c>
       <c r="J13" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K13" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02315464517404087</v>
+        <v>0.02224775097092346</v>
       </c>
       <c r="M13" t="n">
-        <v>10.44153710789104</v>
+        <v>10.37329472977727</v>
       </c>
       <c r="N13" t="n">
-        <v>177.8383152291443</v>
+        <v>176.3448567235371</v>
       </c>
       <c r="O13" t="n">
-        <v>13.33560329453243</v>
+        <v>13.27949007769263</v>
       </c>
       <c r="P13" t="n">
-        <v>354.7944490004944</v>
+        <v>354.7198302841376</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -14983,28 +15111,28 @@
         <v>0.0492</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4166430127960698</v>
+        <v>-0.4043802927885807</v>
       </c>
       <c r="J14" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K14" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04810181506320421</v>
+        <v>0.04631719984771809</v>
       </c>
       <c r="M14" t="n">
-        <v>11.39634981551143</v>
+        <v>11.3390943285575</v>
       </c>
       <c r="N14" t="n">
-        <v>204.6868261628493</v>
+        <v>203.1640873345984</v>
       </c>
       <c r="O14" t="n">
-        <v>14.30688037843503</v>
+        <v>14.25356402218752</v>
       </c>
       <c r="P14" t="n">
-        <v>359.766869454333</v>
+        <v>359.6540255655636</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -15061,28 +15189,28 @@
         <v>0.0406</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.688064373811909</v>
+        <v>-0.6774689986173862</v>
       </c>
       <c r="J15" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K15" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1037997743237005</v>
+        <v>0.1028352849310843</v>
       </c>
       <c r="M15" t="n">
-        <v>12.70322345496766</v>
+        <v>12.62591661780653</v>
       </c>
       <c r="N15" t="n">
-        <v>243.5563375171676</v>
+        <v>241.6096100102499</v>
       </c>
       <c r="O15" t="n">
-        <v>15.60629160041448</v>
+        <v>15.5437965121218</v>
       </c>
       <c r="P15" t="n">
-        <v>366.1956153469443</v>
+        <v>366.0981021128794</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -15120,7 +15248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P209"/>
+  <dimension ref="A1:P211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32261,6 +32389,170 @@
         </is>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>-34.454913122283756,173.00343150632224</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>-34.45564976210434,173.0031968135098</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>-34.45638889556436,173.00309980684503</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>-34.4571286707776,173.00303850055278</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-34.45786728492333,173.0029136264668</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-34.45860831806858,173.00292230784095</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-34.45934177248098,173.0029473962808</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>-34.460068677363296,173.0029508634458</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>-34.460804659631584,173.00293966372035</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-34.461548215737295,173.00293862898445</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>-34.46229790135722,173.00297641028268</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>-34.46304611840633,173.00300771325186</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>-34.46378936103531,173.00302358834404</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>-34.464529249275074,173.00297314830564</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>-34.454913122283756,173.00343150632224</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>-34.45564976210434,173.0031968135098</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>-34.45638889556436,173.00309980684503</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>-34.457128607520964,173.0030350174568</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-34.457867775184894,173.0029406206979</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-34.45860859285104,173.00293743780577</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-34.45934227576193,173.00296295365683</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>-34.46006937661616,173.00296248262742</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-34.46080696526157,173.00297089669553</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>-34.46154892023399,173.00294817247817</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>-34.46229928759796,173.0029995411719</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>-34.46304722209011,173.00304176681578</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>-34.46378998038006,173.0030565709798</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>-34.46453036329245,173.00303247403176</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0006/nzd0006.xlsx
+++ b/data/nzd0006/nzd0006.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P211"/>
+  <dimension ref="A1:P212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11848,6 +11848,60 @@
         <v>356.7</v>
       </c>
       <c r="P211" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17:42+00:00</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>349.98</v>
+      </c>
+      <c r="C212" t="n">
+        <v>329.32</v>
+      </c>
+      <c r="D212" t="n">
+        <v>318.38</v>
+      </c>
+      <c r="E212" t="n">
+        <v>317.46</v>
+      </c>
+      <c r="F212" t="n">
+        <v>313.53</v>
+      </c>
+      <c r="G212" t="n">
+        <v>314.22</v>
+      </c>
+      <c r="H212" t="n">
+        <v>316.25</v>
+      </c>
+      <c r="I212" t="n">
+        <v>320.01</v>
+      </c>
+      <c r="J212" t="n">
+        <v>328.37</v>
+      </c>
+      <c r="K212" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="L212" t="n">
+        <v>348.3</v>
+      </c>
+      <c r="M212" t="n">
+        <v>355.65</v>
+      </c>
+      <c r="N212" t="n">
+        <v>358.7</v>
+      </c>
+      <c r="O212" t="n">
+        <v>358.24</v>
+      </c>
+      <c r="P212" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11864,7 +11918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B214"/>
+  <dimension ref="A1:B215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14007,6 +14061,16 @@
       </c>
       <c r="B214" t="n">
         <v>0.9</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -14175,28 +14239,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.289877356574199</v>
+        <v>-0.2946154208541544</v>
       </c>
       <c r="J2" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K2" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07508671836656888</v>
+        <v>0.07800342481644529</v>
       </c>
       <c r="M2" t="n">
-        <v>6.343001951611255</v>
+        <v>6.34093937239985</v>
       </c>
       <c r="N2" t="n">
-        <v>62.455659531906</v>
+        <v>62.28459654057203</v>
       </c>
       <c r="O2" t="n">
-        <v>7.902889315427998</v>
+        <v>7.892059081163295</v>
       </c>
       <c r="P2" t="n">
-        <v>362.725046358222</v>
+        <v>362.7687549392776</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14253,28 +14317,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3985776508732214</v>
+        <v>-0.4113879030473407</v>
       </c>
       <c r="J3" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K3" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06963394986266458</v>
+        <v>0.07410025442810508</v>
       </c>
       <c r="M3" t="n">
-        <v>8.933471237732057</v>
+        <v>8.958175453140328</v>
       </c>
       <c r="N3" t="n">
-        <v>128.0749021228672</v>
+        <v>128.381181569353</v>
       </c>
       <c r="O3" t="n">
-        <v>11.31701825229893</v>
+        <v>11.3305419803888</v>
       </c>
       <c r="P3" t="n">
-        <v>353.7271921554574</v>
+        <v>353.8453665643325</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14331,28 +14395,28 @@
         <v>0.1034</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.327961245358953</v>
+        <v>-0.3409445564133333</v>
       </c>
       <c r="J4" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K4" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03814969968280613</v>
+        <v>0.041305120979923</v>
       </c>
       <c r="M4" t="n">
-        <v>10.4526619732139</v>
+        <v>10.45553645551119</v>
       </c>
       <c r="N4" t="n">
-        <v>163.6314344805654</v>
+        <v>163.7940416856005</v>
       </c>
       <c r="O4" t="n">
-        <v>12.79185031496872</v>
+        <v>12.79820462743116</v>
       </c>
       <c r="P4" t="n">
-        <v>341.1269832472384</v>
+        <v>341.2467541220221</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14409,28 +14473,28 @@
         <v>0.0706</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4324914837755658</v>
+        <v>-0.4428544120369964</v>
       </c>
       <c r="J5" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K5" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05978313827483683</v>
+        <v>0.06294045283448957</v>
       </c>
       <c r="M5" t="n">
-        <v>10.56917556247147</v>
+        <v>10.56740382817759</v>
       </c>
       <c r="N5" t="n">
-        <v>177.5046640919324</v>
+        <v>177.2610620404366</v>
       </c>
       <c r="O5" t="n">
-        <v>13.3230876335755</v>
+        <v>13.31394239286158</v>
       </c>
       <c r="P5" t="n">
-        <v>340.0819229461576</v>
+        <v>340.177520823925</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14487,28 +14551,28 @@
         <v>0.0582</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5511215407447333</v>
+        <v>-0.5618485065401568</v>
       </c>
       <c r="J6" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K6" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09019308027286765</v>
+        <v>0.09403354712458178</v>
       </c>
       <c r="M6" t="n">
-        <v>10.36534829614521</v>
+        <v>10.3781378733442</v>
       </c>
       <c r="N6" t="n">
-        <v>184.8741161299059</v>
+        <v>184.6383149384824</v>
       </c>
       <c r="O6" t="n">
-        <v>13.59684213815494</v>
+        <v>13.58816819657758</v>
       </c>
       <c r="P6" t="n">
-        <v>339.6443048731585</v>
+        <v>339.743260992419</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14565,28 +14629,28 @@
         <v>0.0497</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3682921047353204</v>
+        <v>-0.3787232908941206</v>
       </c>
       <c r="J7" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K7" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0435439410929066</v>
+        <v>0.04625906909992905</v>
       </c>
       <c r="M7" t="n">
-        <v>10.00852365456021</v>
+        <v>10.02047235147835</v>
       </c>
       <c r="N7" t="n">
-        <v>179.774226522008</v>
+        <v>179.5277673381192</v>
       </c>
       <c r="O7" t="n">
-        <v>13.40799114416503</v>
+        <v>13.39879723475653</v>
       </c>
       <c r="P7" t="n">
-        <v>335.2322692783973</v>
+        <v>335.3284968343757</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14643,28 +14707,28 @@
         <v>0.051</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4113924030220823</v>
+        <v>-0.4171024611419486</v>
       </c>
       <c r="J8" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K8" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04435676096373908</v>
+        <v>0.04597774677735456</v>
       </c>
       <c r="M8" t="n">
-        <v>11.44202229958013</v>
+        <v>11.41871930446679</v>
       </c>
       <c r="N8" t="n">
-        <v>220.015776597867</v>
+        <v>219.1545010087024</v>
       </c>
       <c r="O8" t="n">
-        <v>14.83292879366267</v>
+        <v>14.80386777192712</v>
       </c>
       <c r="P8" t="n">
-        <v>333.2357747448352</v>
+        <v>333.28844995636</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14721,28 +14785,28 @@
         <v>0.0674</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3006915416257423</v>
+        <v>-0.3036943778448764</v>
       </c>
       <c r="J9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02670839376945777</v>
+        <v>0.02751198403538235</v>
       </c>
       <c r="M9" t="n">
-        <v>10.95214434734002</v>
+        <v>10.91383341834468</v>
       </c>
       <c r="N9" t="n">
-        <v>198.8121643793173</v>
+        <v>197.9201085089624</v>
       </c>
       <c r="O9" t="n">
-        <v>14.10007675083073</v>
+        <v>14.0684081725319</v>
       </c>
       <c r="P9" t="n">
-        <v>331.1432100567121</v>
+        <v>331.1709111815862</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -14799,28 +14863,28 @@
         <v>0.0619</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3725280866148421</v>
+        <v>-0.3724858167652245</v>
       </c>
       <c r="J10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04616214083304782</v>
+        <v>0.04663212625009006</v>
       </c>
       <c r="M10" t="n">
-        <v>10.0688632761558</v>
+        <v>10.02140744080966</v>
       </c>
       <c r="N10" t="n">
-        <v>173.0262441143227</v>
+        <v>172.206224464995</v>
       </c>
       <c r="O10" t="n">
-        <v>13.15394405166461</v>
+        <v>13.12273692737132</v>
       </c>
       <c r="P10" t="n">
-        <v>338.0546796492187</v>
+        <v>338.0542897104085</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -14877,28 +14941,28 @@
         <v>0.0475</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2442304587907252</v>
+        <v>-0.2455980384552557</v>
       </c>
       <c r="J11" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K11" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02152173850113215</v>
+        <v>0.02198893650376799</v>
       </c>
       <c r="M11" t="n">
-        <v>10.08925223847102</v>
+        <v>10.04942640954289</v>
       </c>
       <c r="N11" t="n">
-        <v>163.6359809896162</v>
+        <v>162.8708635306152</v>
       </c>
       <c r="O11" t="n">
-        <v>12.79202802489176</v>
+        <v>12.76208695827666</v>
       </c>
       <c r="P11" t="n">
-        <v>343.3736487136125</v>
+        <v>343.3862646181433</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -14955,28 +15019,28 @@
         <v>0.0616</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3844114535755563</v>
+        <v>-0.37825335195893</v>
       </c>
       <c r="J12" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K12" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04886879691778612</v>
+        <v>0.04782578799977888</v>
       </c>
       <c r="M12" t="n">
-        <v>10.92035383182295</v>
+        <v>10.89410524171759</v>
       </c>
       <c r="N12" t="n">
-        <v>173.5428568997539</v>
+        <v>172.9314249897799</v>
       </c>
       <c r="O12" t="n">
-        <v>13.17356659753743</v>
+        <v>13.15033934884495</v>
       </c>
       <c r="P12" t="n">
-        <v>351.6143006681094</v>
+        <v>351.5574922611829</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -15033,28 +15097,28 @@
         <v>0.0581</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2578738968018114</v>
+        <v>-0.2508559651933279</v>
       </c>
       <c r="J13" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K13" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02224775097092346</v>
+        <v>0.02127100626135214</v>
       </c>
       <c r="M13" t="n">
-        <v>10.37329472977727</v>
+        <v>10.35086778209135</v>
       </c>
       <c r="N13" t="n">
-        <v>176.3448567235371</v>
+        <v>175.7831945805845</v>
       </c>
       <c r="O13" t="n">
-        <v>13.27949007769263</v>
+        <v>13.25832548177124</v>
       </c>
       <c r="P13" t="n">
-        <v>354.7198302841376</v>
+        <v>354.6550899567742</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -15111,28 +15175,28 @@
         <v>0.0492</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4043802927885807</v>
+        <v>-0.3955786533742728</v>
       </c>
       <c r="J14" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K14" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04631719984771809</v>
+        <v>0.04478298305269812</v>
       </c>
       <c r="M14" t="n">
-        <v>11.3390943285575</v>
+        <v>11.32180108973983</v>
       </c>
       <c r="N14" t="n">
-        <v>203.1640873345984</v>
+        <v>202.6323568416908</v>
       </c>
       <c r="O14" t="n">
-        <v>14.25356402218752</v>
+        <v>14.2348992564644</v>
       </c>
       <c r="P14" t="n">
-        <v>359.6540255655636</v>
+        <v>359.5728305570049</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -15189,28 +15253,28 @@
         <v>0.0406</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6774689986173862</v>
+        <v>-0.6684569937536606</v>
       </c>
       <c r="J15" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K15" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1028352849310843</v>
+        <v>0.1012035535855843</v>
       </c>
       <c r="M15" t="n">
-        <v>12.62591661780653</v>
+        <v>12.60316770271026</v>
       </c>
       <c r="N15" t="n">
-        <v>241.6096100102499</v>
+        <v>240.9165282771479</v>
       </c>
       <c r="O15" t="n">
-        <v>15.5437965121218</v>
+        <v>15.52148602026069</v>
       </c>
       <c r="P15" t="n">
-        <v>366.0981021128794</v>
+        <v>366.0149664857992</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -15248,7 +15312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P211"/>
+  <dimension ref="A1:P212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32553,6 +32617,88 @@
         </is>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:17:42+00:00</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>-34.45491361243736,173.00345849960556</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>-34.45565007243568,173.00321390214881</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>-34.45638844684637,173.0030750988506</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-34.45712879531383,173.003045357898</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-34.45786854219505,173.00298285360844</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-34.45860919578441,173.0029706366498</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-34.459342610108315,173.0029732889767</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-34.460069507317506,173.00296465443708</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-34.46080734953245,173.00297610219155</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>-34.46155079355114,173.0029735494964</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>-34.462301246550396,173.00303222848615</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>-34.4630478744227,173.00306189432206</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>-34.46379031968727,173.00307464067484</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>-34.4645306780738,173.0030492376317</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0006/nzd0006.xlsx
+++ b/data/nzd0006/nzd0006.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P212"/>
+  <dimension ref="A1:P213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11902,6 +11902,60 @@
         <v>358.24</v>
       </c>
       <c r="P212" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>354.65</v>
+      </c>
+      <c r="C213" t="n">
+        <v>331.81</v>
+      </c>
+      <c r="D213" t="n">
+        <v>320.39</v>
+      </c>
+      <c r="E213" t="n">
+        <v>320.11</v>
+      </c>
+      <c r="F213" t="n">
+        <v>315.93</v>
+      </c>
+      <c r="G213" t="n">
+        <v>316.88</v>
+      </c>
+      <c r="H213" t="n">
+        <v>317.92</v>
+      </c>
+      <c r="I213" t="n">
+        <v>321.86</v>
+      </c>
+      <c r="J213" t="n">
+        <v>331.12</v>
+      </c>
+      <c r="K213" t="n">
+        <v>338.59</v>
+      </c>
+      <c r="L213" t="n">
+        <v>351.41</v>
+      </c>
+      <c r="M213" t="n">
+        <v>358.91</v>
+      </c>
+      <c r="N213" t="n">
+        <v>364.72</v>
+      </c>
+      <c r="O213" t="n">
+        <v>365.31</v>
+      </c>
+      <c r="P213" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11918,7 +11972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B215"/>
+  <dimension ref="A1:B216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14071,6 +14125,16 @@
       </c>
       <c r="B215" t="n">
         <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -14239,28 +14303,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2946154208541544</v>
+        <v>-0.2949702221168375</v>
       </c>
       <c r="J2" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K2" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07800342481644529</v>
+        <v>0.07895708795158685</v>
       </c>
       <c r="M2" t="n">
-        <v>6.34093937239985</v>
+        <v>6.313122714576042</v>
       </c>
       <c r="N2" t="n">
-        <v>62.28459654057203</v>
+        <v>61.99150995617724</v>
       </c>
       <c r="O2" t="n">
-        <v>7.892059081163295</v>
+        <v>7.873468737232481</v>
       </c>
       <c r="P2" t="n">
-        <v>362.7687549392776</v>
+        <v>362.7720415918367</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14317,28 +14381,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4113879030473407</v>
+        <v>-0.4216022237462944</v>
       </c>
       <c r="J3" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K3" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07410025442810508</v>
+        <v>0.07798170202479116</v>
       </c>
       <c r="M3" t="n">
-        <v>8.958175453140328</v>
+        <v>8.968747603893704</v>
       </c>
       <c r="N3" t="n">
-        <v>128.381181569353</v>
+        <v>128.3629643963788</v>
       </c>
       <c r="O3" t="n">
-        <v>11.3305419803888</v>
+        <v>11.32973805506459</v>
       </c>
       <c r="P3" t="n">
-        <v>353.8453665643325</v>
+        <v>353.9399855152633</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14395,28 +14459,28 @@
         <v>0.1034</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3409445564133333</v>
+        <v>-0.351765835129332</v>
       </c>
       <c r="J4" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K4" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L4" t="n">
-        <v>0.041305120979923</v>
+        <v>0.04413601954966551</v>
       </c>
       <c r="M4" t="n">
-        <v>10.45553645551119</v>
+        <v>10.44958720303755</v>
       </c>
       <c r="N4" t="n">
-        <v>163.7940416856005</v>
+        <v>163.6806605269554</v>
       </c>
       <c r="O4" t="n">
-        <v>12.79820462743116</v>
+        <v>12.79377428779152</v>
       </c>
       <c r="P4" t="n">
-        <v>341.2467541220221</v>
+        <v>341.3469955448259</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14473,28 +14537,28 @@
         <v>0.0706</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4428544120369964</v>
+        <v>-0.4505356895266827</v>
       </c>
       <c r="J5" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K5" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06294045283448957</v>
+        <v>0.06554323904949333</v>
       </c>
       <c r="M5" t="n">
-        <v>10.56740382817759</v>
+        <v>10.55583105812399</v>
       </c>
       <c r="N5" t="n">
-        <v>177.2610620404366</v>
+        <v>176.7570856079874</v>
       </c>
       <c r="O5" t="n">
-        <v>13.31394239286158</v>
+        <v>13.29500227935247</v>
       </c>
       <c r="P5" t="n">
-        <v>340.177520823925</v>
+        <v>340.24867527847</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14551,28 +14615,28 @@
         <v>0.0582</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5618485065401568</v>
+        <v>-0.5701013913604632</v>
       </c>
       <c r="J6" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K6" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09403354712458178</v>
+        <v>0.09730976466673102</v>
       </c>
       <c r="M6" t="n">
-        <v>10.3781378733442</v>
+        <v>10.37627741986411</v>
       </c>
       <c r="N6" t="n">
-        <v>184.6383149384824</v>
+        <v>184.1508154542497</v>
       </c>
       <c r="O6" t="n">
-        <v>13.58816819657758</v>
+        <v>13.57021795898097</v>
       </c>
       <c r="P6" t="n">
-        <v>339.743260992419</v>
+        <v>339.8197104526293</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14629,28 +14693,28 @@
         <v>0.0497</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3787232908941206</v>
+        <v>-0.3864657357335602</v>
       </c>
       <c r="J7" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K7" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04625906909992905</v>
+        <v>0.04848708805049606</v>
       </c>
       <c r="M7" t="n">
-        <v>10.02047235147835</v>
+        <v>10.01681062796112</v>
       </c>
       <c r="N7" t="n">
-        <v>179.5277673381192</v>
+        <v>179.0184100687617</v>
       </c>
       <c r="O7" t="n">
-        <v>13.39879723475653</v>
+        <v>13.37977615914264</v>
       </c>
       <c r="P7" t="n">
-        <v>335.3284968343757</v>
+        <v>335.4002179042284</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14707,28 +14771,28 @@
         <v>0.051</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4171024611419486</v>
+        <v>-0.421131910021294</v>
       </c>
       <c r="J8" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K8" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04597774677735456</v>
+        <v>0.04729372293877654</v>
       </c>
       <c r="M8" t="n">
-        <v>11.41871930446679</v>
+        <v>11.38643425888257</v>
       </c>
       <c r="N8" t="n">
-        <v>219.1545010087024</v>
+        <v>218.2121589146855</v>
       </c>
       <c r="O8" t="n">
-        <v>14.80386777192712</v>
+        <v>14.77200592047964</v>
       </c>
       <c r="P8" t="n">
-        <v>333.28844995636</v>
+        <v>333.3257762002709</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14785,28 +14849,28 @@
         <v>0.0674</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3036943778448764</v>
+        <v>-0.3049194304218431</v>
       </c>
       <c r="J9" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K9" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02751198403538235</v>
+        <v>0.02801945934413719</v>
       </c>
       <c r="M9" t="n">
-        <v>10.91383341834468</v>
+        <v>10.86783193790509</v>
       </c>
       <c r="N9" t="n">
-        <v>197.9201085089624</v>
+        <v>196.9949718078734</v>
       </c>
       <c r="O9" t="n">
-        <v>14.0684081725319</v>
+        <v>14.03548972454732</v>
       </c>
       <c r="P9" t="n">
-        <v>331.1709111815862</v>
+        <v>331.1822592871612</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -14863,28 +14927,28 @@
         <v>0.0619</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3724858167652245</v>
+        <v>-0.3699110598542156</v>
       </c>
       <c r="J10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04663212625009006</v>
+        <v>0.04648565850703812</v>
       </c>
       <c r="M10" t="n">
-        <v>10.02140744080966</v>
+        <v>9.990025356518155</v>
       </c>
       <c r="N10" t="n">
-        <v>172.206224464995</v>
+        <v>171.4312519936955</v>
       </c>
       <c r="O10" t="n">
-        <v>13.12273692737132</v>
+        <v>13.09317577953093</v>
       </c>
       <c r="P10" t="n">
-        <v>338.0542897104085</v>
+        <v>338.0304388049003</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -14941,28 +15005,28 @@
         <v>0.0475</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2455980384552557</v>
+        <v>-0.2441044498133839</v>
       </c>
       <c r="J11" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K11" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02198893650376799</v>
+        <v>0.0219569912788945</v>
       </c>
       <c r="M11" t="n">
-        <v>10.04942640954289</v>
+        <v>10.00866954079247</v>
       </c>
       <c r="N11" t="n">
-        <v>162.8708635306152</v>
+        <v>162.1151633997367</v>
       </c>
       <c r="O11" t="n">
-        <v>12.76208695827666</v>
+        <v>12.73244530322972</v>
       </c>
       <c r="P11" t="n">
-        <v>343.3862646181433</v>
+        <v>343.3724289657704</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -15019,28 +15083,28 @@
         <v>0.0616</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.37825335195893</v>
+        <v>-0.3693784289314517</v>
       </c>
       <c r="J12" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K12" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04782578799977888</v>
+        <v>0.04606904318934113</v>
       </c>
       <c r="M12" t="n">
-        <v>10.89410524171759</v>
+        <v>10.87917616034597</v>
       </c>
       <c r="N12" t="n">
-        <v>172.9314249897799</v>
+        <v>172.5591258086467</v>
       </c>
       <c r="O12" t="n">
-        <v>13.15033934884495</v>
+        <v>13.13617622478652</v>
       </c>
       <c r="P12" t="n">
-        <v>351.5574922611829</v>
+        <v>351.4752806358384</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -15097,28 +15161,28 @@
         <v>0.0581</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2508559651933279</v>
+        <v>-0.24101583239862</v>
       </c>
       <c r="J13" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K13" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02127100626135214</v>
+        <v>0.01981577174767435</v>
       </c>
       <c r="M13" t="n">
-        <v>10.35086778209135</v>
+        <v>10.33922470321287</v>
       </c>
       <c r="N13" t="n">
-        <v>175.7831945805845</v>
+        <v>175.4991373706515</v>
       </c>
       <c r="O13" t="n">
-        <v>13.25832548177124</v>
+        <v>13.24760874160509</v>
       </c>
       <c r="P13" t="n">
-        <v>354.6550899567742</v>
+        <v>354.5639372438825</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -15175,28 +15239,28 @@
         <v>0.0492</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3955786533742728</v>
+        <v>-0.3814872539630107</v>
       </c>
       <c r="J14" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K14" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04478298305269812</v>
+        <v>0.0419914242538193</v>
       </c>
       <c r="M14" t="n">
-        <v>11.32180108973983</v>
+        <v>11.32697909022693</v>
       </c>
       <c r="N14" t="n">
-        <v>202.6323568416908</v>
+        <v>202.7944092680314</v>
       </c>
       <c r="O14" t="n">
-        <v>14.2348992564644</v>
+        <v>14.24059020083197</v>
       </c>
       <c r="P14" t="n">
-        <v>359.5728305570049</v>
+        <v>359.4422968221891</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -15253,28 +15317,28 @@
         <v>0.0406</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6684569937536606</v>
+        <v>-0.6531811058187995</v>
       </c>
       <c r="J15" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K15" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1012035535855843</v>
+        <v>0.09754273131869684</v>
       </c>
       <c r="M15" t="n">
-        <v>12.60316770271026</v>
+        <v>12.60601502386113</v>
       </c>
       <c r="N15" t="n">
-        <v>240.9165282771479</v>
+        <v>241.0938235201612</v>
       </c>
       <c r="O15" t="n">
-        <v>15.52148602026069</v>
+        <v>15.52719625431975</v>
       </c>
       <c r="P15" t="n">
-        <v>366.0149664857992</v>
+        <v>365.8734604049219</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -15312,7 +15376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P212"/>
+  <dimension ref="A1:P213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32699,6 +32763,88 @@
         </is>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>-34.45491453541203,173.0035093297004</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>-34.455650564612334,173.00324100451286</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>-34.4563888441696,173.00309697685447</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-34.45712931915242,173.00307420228697</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-34.457869016627015,173.00300897705867</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-34.45860972161402,173.0029995903961</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-34.459343197851965,173.00299145738126</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>-34.4600707163031,173.00298474367688</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>-34.460809551080125,173.00300592534683</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>-34.46155326728238,173.00300706017606</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>-34.462303270575156,173.00306600175927</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>-34.46304902393045,173.00309736225273</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>-34.46379155016452,173.00314017053398</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>-34.46453212317685,173.00312619779677</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0006/nzd0006.xlsx
+++ b/data/nzd0006/nzd0006.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P213"/>
+  <dimension ref="A1:P214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11958,6 +11958,60 @@
       <c r="P213" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>353.87</v>
+      </c>
+      <c r="C214" t="n">
+        <v>332.01</v>
+      </c>
+      <c r="D214" t="n">
+        <v>318.75</v>
+      </c>
+      <c r="E214" t="n">
+        <v>319.44</v>
+      </c>
+      <c r="F214" t="n">
+        <v>319.94</v>
+      </c>
+      <c r="G214" t="n">
+        <v>320.25</v>
+      </c>
+      <c r="H214" t="n">
+        <v>321.01</v>
+      </c>
+      <c r="I214" t="n">
+        <v>322.33</v>
+      </c>
+      <c r="J214" t="n">
+        <v>332.41</v>
+      </c>
+      <c r="K214" t="n">
+        <v>340.71</v>
+      </c>
+      <c r="L214" t="n">
+        <v>352.77</v>
+      </c>
+      <c r="M214" t="n">
+        <v>360.78</v>
+      </c>
+      <c r="N214" t="n">
+        <v>364.15</v>
+      </c>
+      <c r="O214" t="n">
+        <v>363.62</v>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11972,7 +12026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B216"/>
+  <dimension ref="A1:B217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14135,6 +14189,16 @@
       </c>
       <c r="B216" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>
@@ -14303,28 +14367,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2949702221168375</v>
+        <v>-0.2959915453263013</v>
       </c>
       <c r="J2" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K2" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07895708795158685</v>
+        <v>0.08025168749501932</v>
       </c>
       <c r="M2" t="n">
-        <v>6.313122714576042</v>
+        <v>6.28941480883716</v>
       </c>
       <c r="N2" t="n">
-        <v>61.99150995617724</v>
+        <v>61.70634503970263</v>
       </c>
       <c r="O2" t="n">
-        <v>7.873468737232481</v>
+        <v>7.855338633038211</v>
       </c>
       <c r="P2" t="n">
-        <v>362.7720415918367</v>
+        <v>362.7815707334684</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14381,28 +14445,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4216022237462944</v>
+        <v>-0.4313969580296774</v>
       </c>
       <c r="J3" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K3" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07798170202479116</v>
+        <v>0.08184594942390111</v>
       </c>
       <c r="M3" t="n">
-        <v>8.968747603893704</v>
+        <v>8.976433681508594</v>
       </c>
       <c r="N3" t="n">
-        <v>128.3629643963788</v>
+        <v>128.300664302284</v>
       </c>
       <c r="O3" t="n">
-        <v>11.32973805506459</v>
+        <v>11.32698831562406</v>
       </c>
       <c r="P3" t="n">
-        <v>353.9399855152633</v>
+        <v>354.0313722666525</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14459,28 +14523,28 @@
         <v>0.1034</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.351765835129332</v>
+        <v>-0.3638295940489265</v>
       </c>
       <c r="J4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K4" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04413601954966551</v>
+        <v>0.04733260824364371</v>
       </c>
       <c r="M4" t="n">
-        <v>10.44958720303755</v>
+        <v>10.44827993961786</v>
       </c>
       <c r="N4" t="n">
-        <v>163.6806605269554</v>
+        <v>163.7318963811441</v>
       </c>
       <c r="O4" t="n">
-        <v>12.79377428779152</v>
+        <v>12.79577650559528</v>
       </c>
       <c r="P4" t="n">
-        <v>341.3469955448259</v>
+        <v>341.4595527317089</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14537,28 +14601,28 @@
         <v>0.0706</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4505356895266827</v>
+        <v>-0.458624896292738</v>
       </c>
       <c r="J5" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K5" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06554323904949333</v>
+        <v>0.06831246870770968</v>
       </c>
       <c r="M5" t="n">
-        <v>10.55583105812399</v>
+        <v>10.54689419725089</v>
       </c>
       <c r="N5" t="n">
-        <v>176.7570856079874</v>
+        <v>176.2957898083434</v>
       </c>
       <c r="O5" t="n">
-        <v>13.29500227935247</v>
+        <v>13.27764247930872</v>
       </c>
       <c r="P5" t="n">
-        <v>340.24867527847</v>
+        <v>340.3241491306724</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14615,28 +14679,28 @@
         <v>0.0582</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5701013913604632</v>
+        <v>-0.5744895871747133</v>
       </c>
       <c r="J6" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K6" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09730976466673102</v>
+        <v>0.09958142538414172</v>
       </c>
       <c r="M6" t="n">
-        <v>10.37627741986411</v>
+        <v>10.35219320105353</v>
       </c>
       <c r="N6" t="n">
-        <v>184.1508154542497</v>
+        <v>183.3947142774177</v>
       </c>
       <c r="O6" t="n">
-        <v>13.57021795898097</v>
+        <v>13.54233045961505</v>
       </c>
       <c r="P6" t="n">
-        <v>339.8197104526293</v>
+        <v>339.8606531620813</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14693,28 +14757,28 @@
         <v>0.0497</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3864657357335602</v>
+        <v>-0.3909579547806727</v>
       </c>
       <c r="J7" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K7" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04848708805049606</v>
+        <v>0.05004805762089437</v>
       </c>
       <c r="M7" t="n">
-        <v>10.01681062796112</v>
+        <v>9.995212731778091</v>
       </c>
       <c r="N7" t="n">
-        <v>179.0184100687617</v>
+        <v>178.2916076191744</v>
       </c>
       <c r="O7" t="n">
-        <v>13.37977615914264</v>
+        <v>13.35258804948218</v>
       </c>
       <c r="P7" t="n">
-        <v>335.4002179042284</v>
+        <v>335.4421311704148</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14771,28 +14835,28 @@
         <v>0.051</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.421131910021294</v>
+        <v>-0.4222311973644124</v>
       </c>
       <c r="J8" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K8" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04729372293877654</v>
+        <v>0.04802146080968428</v>
       </c>
       <c r="M8" t="n">
-        <v>11.38643425888257</v>
+        <v>11.33876803215355</v>
       </c>
       <c r="N8" t="n">
-        <v>218.2121589146855</v>
+        <v>217.1944949149031</v>
       </c>
       <c r="O8" t="n">
-        <v>14.77200592047964</v>
+        <v>14.73751997165409</v>
       </c>
       <c r="P8" t="n">
-        <v>333.3257762002709</v>
+        <v>333.3360327622382</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14849,28 +14913,28 @@
         <v>0.0674</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3049194304218431</v>
+        <v>-0.3056573644079945</v>
       </c>
       <c r="J9" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K9" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02801945934413719</v>
+        <v>0.02844941485524455</v>
       </c>
       <c r="M9" t="n">
-        <v>10.86783193790509</v>
+        <v>10.82013585444687</v>
       </c>
       <c r="N9" t="n">
-        <v>196.9949718078734</v>
+        <v>196.0731798234801</v>
       </c>
       <c r="O9" t="n">
-        <v>14.03548972454732</v>
+        <v>14.00261332121544</v>
       </c>
       <c r="P9" t="n">
-        <v>331.1822592871612</v>
+        <v>331.1891443529304</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -14927,28 +14991,28 @@
         <v>0.0619</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3699110598542156</v>
+        <v>-0.3661673663463208</v>
       </c>
       <c r="J10" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K10" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04648565850703812</v>
+        <v>0.04604641003203325</v>
       </c>
       <c r="M10" t="n">
-        <v>9.990025356518155</v>
+        <v>9.96641188803577</v>
       </c>
       <c r="N10" t="n">
-        <v>171.4312519936955</v>
+        <v>170.7053481825371</v>
       </c>
       <c r="O10" t="n">
-        <v>13.09317577953093</v>
+        <v>13.06542567934689</v>
       </c>
       <c r="P10" t="n">
-        <v>338.0304388049003</v>
+        <v>337.9955094257069</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -15005,28 +15069,28 @@
         <v>0.0475</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2441044498133839</v>
+        <v>-0.2406877633975782</v>
       </c>
       <c r="J11" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K11" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0219569912788945</v>
+        <v>0.02157909859895168</v>
       </c>
       <c r="M11" t="n">
-        <v>10.00866954079247</v>
+        <v>9.976587361070903</v>
       </c>
       <c r="N11" t="n">
-        <v>162.1151633997367</v>
+        <v>161.4198091405882</v>
       </c>
       <c r="O11" t="n">
-        <v>12.73244530322972</v>
+        <v>12.70510956822444</v>
       </c>
       <c r="P11" t="n">
-        <v>343.3724289657704</v>
+        <v>343.3405506255294</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -15083,28 +15147,28 @@
         <v>0.0616</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3693784289314517</v>
+        <v>-0.3593780497775319</v>
       </c>
       <c r="J12" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K12" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04606904318934113</v>
+        <v>0.04403376838668871</v>
       </c>
       <c r="M12" t="n">
-        <v>10.87917616034597</v>
+        <v>10.86833001736754</v>
       </c>
       <c r="N12" t="n">
-        <v>172.5591258086467</v>
+        <v>172.3122596748501</v>
       </c>
       <c r="O12" t="n">
-        <v>13.13617622478652</v>
+        <v>13.12677643882344</v>
       </c>
       <c r="P12" t="n">
-        <v>351.4752806358384</v>
+        <v>351.3819751783245</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -15161,28 +15225,28 @@
         <v>0.0581</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.24101583239862</v>
+        <v>-0.2296249001165525</v>
       </c>
       <c r="J13" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K13" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01981577174767435</v>
+        <v>0.01813844876509274</v>
       </c>
       <c r="M13" t="n">
-        <v>10.33922470321287</v>
+        <v>10.33586325465173</v>
       </c>
       <c r="N13" t="n">
-        <v>175.4991373706515</v>
+        <v>175.4060047559699</v>
       </c>
       <c r="O13" t="n">
-        <v>13.24760874160509</v>
+        <v>13.24409320247973</v>
       </c>
       <c r="P13" t="n">
-        <v>354.5639372438825</v>
+        <v>354.457657658706</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -15239,28 +15303,28 @@
         <v>0.0492</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3814872539630107</v>
+        <v>-0.3681105370814663</v>
       </c>
       <c r="J14" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K14" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0419914242538193</v>
+        <v>0.03943347165061062</v>
       </c>
       <c r="M14" t="n">
-        <v>11.32697909022693</v>
+        <v>11.33134422313928</v>
       </c>
       <c r="N14" t="n">
-        <v>202.7944092680314</v>
+        <v>202.8501434312684</v>
       </c>
       <c r="O14" t="n">
-        <v>14.24059020083197</v>
+        <v>14.24254694327066</v>
       </c>
       <c r="P14" t="n">
-        <v>359.4422968221891</v>
+        <v>359.3174894854417</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -15317,28 +15381,28 @@
         <v>0.0406</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6531811058187995</v>
+        <v>-0.6396162572818181</v>
       </c>
       <c r="J15" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K15" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09754273131869684</v>
+        <v>0.09446809494929398</v>
       </c>
       <c r="M15" t="n">
-        <v>12.60601502386113</v>
+        <v>12.60252155516224</v>
       </c>
       <c r="N15" t="n">
-        <v>241.0938235201612</v>
+        <v>240.998295778009</v>
       </c>
       <c r="O15" t="n">
-        <v>15.52719625431975</v>
+        <v>15.52411980686857</v>
       </c>
       <c r="P15" t="n">
-        <v>365.8734604049219</v>
+        <v>365.7468977637092</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -15376,7 +15440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P213"/>
+  <dimension ref="A1:P214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32845,6 +32909,88 @@
         </is>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>-34.454914381255,173.0035008398772</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>-34.45565060414434,173.0032431814096</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>-34.45638851998576,173.00307912614483</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-34.45712918671086,173.0030669095546</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-34.45786980931132,173.00305262499077</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-34.45861038778681,173.00303627239853</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-34.45934428534656,173.00302507437002</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>-34.46007102345027,173.0029898474298</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-34.46081058380363,173.0030199151184</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>-34.461554964464824,173.0030300513231</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>-34.46230415567629,173.00308077077952</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>-34.463049683306025,173.00311770735453</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>-34.46379143365903,173.00313396587947</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>-34.46453177774644,173.00310780137804</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0006/nzd0006.xlsx
+++ b/data/nzd0006/nzd0006.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P214"/>
+  <dimension ref="A1:P215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12012,6 +12012,60 @@
       <c r="P214" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>351.47</v>
+      </c>
+      <c r="C215" t="n">
+        <v>331.35</v>
+      </c>
+      <c r="D215" t="n">
+        <v>319.39</v>
+      </c>
+      <c r="E215" t="n">
+        <v>320.04</v>
+      </c>
+      <c r="F215" t="n">
+        <v>318.85</v>
+      </c>
+      <c r="G215" t="n">
+        <v>318.32</v>
+      </c>
+      <c r="H215" t="n">
+        <v>319.43</v>
+      </c>
+      <c r="I215" t="n">
+        <v>322.3</v>
+      </c>
+      <c r="J215" t="n">
+        <v>331.02</v>
+      </c>
+      <c r="K215" t="n">
+        <v>339.62</v>
+      </c>
+      <c r="L215" t="n">
+        <v>351.52</v>
+      </c>
+      <c r="M215" t="n">
+        <v>358.69</v>
+      </c>
+      <c r="N215" t="n">
+        <v>359.75</v>
+      </c>
+      <c r="O215" t="n">
+        <v>357.29</v>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12026,7 +12080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B217"/>
+  <dimension ref="A1:B218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14199,6 +14253,16 @@
       </c>
       <c r="B217" t="n">
         <v>0.78</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -14367,28 +14431,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2959915453263013</v>
+        <v>-0.2991207490516472</v>
       </c>
       <c r="J2" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K2" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08025168749501932</v>
+        <v>0.08255389499764021</v>
       </c>
       <c r="M2" t="n">
-        <v>6.28941480883716</v>
+        <v>6.278083383629184</v>
       </c>
       <c r="N2" t="n">
-        <v>61.70634503970263</v>
+        <v>61.47440577615614</v>
       </c>
       <c r="O2" t="n">
-        <v>7.855338633038211</v>
+        <v>7.840561572754603</v>
       </c>
       <c r="P2" t="n">
-        <v>362.7815707334684</v>
+        <v>362.8107967026659</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14445,28 +14509,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4313969580296774</v>
+        <v>-0.44149397097784</v>
       </c>
       <c r="J3" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K3" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08184594942390111</v>
+        <v>0.08586762071980181</v>
       </c>
       <c r="M3" t="n">
-        <v>8.976433681508594</v>
+        <v>8.985485458029412</v>
       </c>
       <c r="N3" t="n">
-        <v>128.300664302284</v>
+        <v>128.2884284233705</v>
       </c>
       <c r="O3" t="n">
-        <v>11.32698831562406</v>
+        <v>11.32644818216949</v>
       </c>
       <c r="P3" t="n">
-        <v>354.0313722666525</v>
+        <v>354.1256758068856</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14523,28 +14587,28 @@
         <v>0.1034</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3638295940489265</v>
+        <v>-0.3749751167459711</v>
       </c>
       <c r="J4" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K4" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04733260824364371</v>
+        <v>0.05042991110296957</v>
       </c>
       <c r="M4" t="n">
-        <v>10.44827993961786</v>
+        <v>10.44329655280883</v>
       </c>
       <c r="N4" t="n">
-        <v>163.7318963811441</v>
+        <v>163.6824017667057</v>
       </c>
       <c r="O4" t="n">
-        <v>12.79577650559528</v>
+        <v>12.79384233788683</v>
       </c>
       <c r="P4" t="n">
-        <v>341.4595527317089</v>
+        <v>341.563649087084</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14601,28 +14665,28 @@
         <v>0.0706</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.458624896292738</v>
+        <v>-0.4659381537700765</v>
       </c>
       <c r="J5" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K5" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06831246870770968</v>
+        <v>0.07093965629913312</v>
       </c>
       <c r="M5" t="n">
-        <v>10.54689419725089</v>
+        <v>10.53409984314457</v>
       </c>
       <c r="N5" t="n">
-        <v>176.2957898083434</v>
+        <v>175.7800806550038</v>
       </c>
       <c r="O5" t="n">
-        <v>13.27764247930872</v>
+        <v>13.25820804841302</v>
       </c>
       <c r="P5" t="n">
-        <v>340.3241491306724</v>
+        <v>340.3924531007959</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14679,28 +14743,28 @@
         <v>0.0582</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5744895871747133</v>
+        <v>-0.5797139367560338</v>
       </c>
       <c r="J6" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K6" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09958142538414172</v>
+        <v>0.1021129640239617</v>
       </c>
       <c r="M6" t="n">
-        <v>10.35219320105353</v>
+        <v>10.33319963727136</v>
       </c>
       <c r="N6" t="n">
-        <v>183.3947142774177</v>
+        <v>182.6949607794664</v>
       </c>
       <c r="O6" t="n">
-        <v>13.54233045961505</v>
+        <v>13.51646998219085</v>
       </c>
       <c r="P6" t="n">
-        <v>339.8606531620813</v>
+        <v>339.9094472622238</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14757,28 +14821,28 @@
         <v>0.0497</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3909579547806727</v>
+        <v>-0.3970387622577638</v>
       </c>
       <c r="J7" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K7" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05004805762089437</v>
+        <v>0.0520012898770551</v>
       </c>
       <c r="M7" t="n">
-        <v>9.995212731778091</v>
+        <v>9.982749668494588</v>
       </c>
       <c r="N7" t="n">
-        <v>178.2916076191744</v>
+        <v>177.6714776185856</v>
       </c>
       <c r="O7" t="n">
-        <v>13.35258804948218</v>
+        <v>13.32934648130154</v>
       </c>
       <c r="P7" t="n">
-        <v>335.4421311704148</v>
+        <v>335.4989243700976</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14835,28 +14899,28 @@
         <v>0.051</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4222311973644124</v>
+        <v>-0.424703713474155</v>
       </c>
       <c r="J8" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K8" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04802146080968428</v>
+        <v>0.0490460980522498</v>
       </c>
       <c r="M8" t="n">
-        <v>11.33876803215355</v>
+        <v>11.29872621803871</v>
       </c>
       <c r="N8" t="n">
-        <v>217.1944949149031</v>
+        <v>216.2147843709529</v>
       </c>
       <c r="O8" t="n">
-        <v>14.73751997165409</v>
+        <v>14.70424375379274</v>
       </c>
       <c r="P8" t="n">
-        <v>333.3360327622382</v>
+        <v>333.3591254356486</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14913,28 +14977,28 @@
         <v>0.0674</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3056573644079945</v>
+        <v>-0.306389450938162</v>
       </c>
       <c r="J9" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K9" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02844941485524455</v>
+        <v>0.02887939948853002</v>
       </c>
       <c r="M9" t="n">
-        <v>10.82013585444687</v>
+        <v>10.77287620327079</v>
       </c>
       <c r="N9" t="n">
-        <v>196.0731798234801</v>
+        <v>195.1600374542979</v>
       </c>
       <c r="O9" t="n">
-        <v>14.00261332121544</v>
+        <v>13.96996912860934</v>
       </c>
       <c r="P9" t="n">
-        <v>331.1891443529304</v>
+        <v>331.1959818554578</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -14991,28 +15055,28 @@
         <v>0.0619</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3661673663463208</v>
+        <v>-0.3637628218498085</v>
       </c>
       <c r="J10" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K10" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04604641003203325</v>
+        <v>0.04592804231322989</v>
       </c>
       <c r="M10" t="n">
-        <v>9.96641188803577</v>
+        <v>9.934714293069566</v>
       </c>
       <c r="N10" t="n">
-        <v>170.7053481825371</v>
+        <v>169.9409669652755</v>
       </c>
       <c r="O10" t="n">
-        <v>13.06542567934689</v>
+        <v>13.03614080030112</v>
       </c>
       <c r="P10" t="n">
-        <v>337.9955094257069</v>
+        <v>337.9730515899258</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -15069,28 +15133,28 @@
         <v>0.0475</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2406877633975782</v>
+        <v>-0.2383367593647405</v>
       </c>
       <c r="J11" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K11" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02157909859895168</v>
+        <v>0.02138664914130628</v>
       </c>
       <c r="M11" t="n">
-        <v>9.976587361070903</v>
+        <v>9.940155165369561</v>
       </c>
       <c r="N11" t="n">
-        <v>161.4198091405882</v>
+        <v>160.6973515400614</v>
       </c>
       <c r="O11" t="n">
-        <v>12.70510956822444</v>
+        <v>12.67664591049467</v>
       </c>
       <c r="P11" t="n">
-        <v>343.3405506255294</v>
+        <v>343.3185928441007</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -15147,28 +15211,28 @@
         <v>0.0616</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3593780497775319</v>
+        <v>-0.3507735242832324</v>
       </c>
       <c r="J12" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K12" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04403376838668871</v>
+        <v>0.04236911015876998</v>
       </c>
       <c r="M12" t="n">
-        <v>10.86833001736754</v>
+        <v>10.85191552678685</v>
       </c>
       <c r="N12" t="n">
-        <v>172.3122596748501</v>
+        <v>171.9335709820392</v>
       </c>
       <c r="O12" t="n">
-        <v>13.12677643882344</v>
+        <v>13.11234422145938</v>
       </c>
       <c r="P12" t="n">
-        <v>351.3819751783245</v>
+        <v>351.3016110924009</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -15225,28 +15289,28 @@
         <v>0.0581</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2296249001165525</v>
+        <v>-0.2204300708743276</v>
       </c>
       <c r="J13" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K13" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01813844876509274</v>
+        <v>0.01686907127945714</v>
       </c>
       <c r="M13" t="n">
-        <v>10.33586325465173</v>
+        <v>10.32661293408101</v>
       </c>
       <c r="N13" t="n">
-        <v>175.4060047559699</v>
+        <v>175.0733869762375</v>
       </c>
       <c r="O13" t="n">
-        <v>13.24409320247973</v>
+        <v>13.23153003156617</v>
       </c>
       <c r="P13" t="n">
-        <v>354.457657658706</v>
+        <v>354.3717802854837</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -15303,28 +15367,28 @@
         <v>0.0492</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3681105370814663</v>
+        <v>-0.3590451214423012</v>
       </c>
       <c r="J14" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K14" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03943347165061062</v>
+        <v>0.03788984505193715</v>
       </c>
       <c r="M14" t="n">
-        <v>11.33134422313928</v>
+        <v>11.3175799962157</v>
       </c>
       <c r="N14" t="n">
-        <v>202.8501434312684</v>
+        <v>202.3756687994528</v>
       </c>
       <c r="O14" t="n">
-        <v>14.24254694327066</v>
+        <v>14.22588024691101</v>
       </c>
       <c r="P14" t="n">
-        <v>359.3174894854417</v>
+        <v>359.2328208024514</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -15381,28 +15445,28 @@
         <v>0.0406</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6396162572818181</v>
+        <v>-0.632083869487238</v>
       </c>
       <c r="J15" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K15" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09446809494929398</v>
+        <v>0.09324518136688165</v>
       </c>
       <c r="M15" t="n">
-        <v>12.60252155516224</v>
+        <v>12.57523361302438</v>
       </c>
       <c r="N15" t="n">
-        <v>240.998295778009</v>
+        <v>240.1989787285861</v>
       </c>
       <c r="O15" t="n">
-        <v>15.52411980686857</v>
+        <v>15.49835406514466</v>
       </c>
       <c r="P15" t="n">
-        <v>365.7468977637092</v>
+        <v>365.6765471719963</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -15440,7 +15504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P214"/>
+  <dimension ref="A1:P215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32991,6 +33055,88 @@
         </is>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>-34.45491390692194,173.00347471734446</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>-34.455650473688586,173.00323599765042</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>-34.45638864649684,173.00308609227542</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>-34.457129305315256,173.00307344035969</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>-34.45786959384506,173.0030407605902</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-34.45861000627081,173.00301526460478</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-34.459343729282516,173.0030078851006</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-34.46007100384513,173.00298952165832</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-34.46080947102397,173.00300484086844</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>-34.461554091857394,173.00301823040303</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>-34.462303342164276,173.00306719631234</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>-34.463048946356636,173.0030949687114</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>-34.46379053430792,173.0030860703013</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>-34.46453048389078,173.0030388964499</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0006/nzd0006.xlsx
+++ b/data/nzd0006/nzd0006.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P215"/>
+  <dimension ref="A1:P217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12064,6 +12064,114 @@
         <v>357.29</v>
       </c>
       <c r="P215" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>352.36</v>
+      </c>
+      <c r="C216" t="n">
+        <v>330.21</v>
+      </c>
+      <c r="D216" t="n">
+        <v>317.57</v>
+      </c>
+      <c r="E216" t="n">
+        <v>318.99</v>
+      </c>
+      <c r="F216" t="n">
+        <v>319.33</v>
+      </c>
+      <c r="G216" t="n">
+        <v>318.49</v>
+      </c>
+      <c r="H216" t="n">
+        <v>316.58</v>
+      </c>
+      <c r="I216" t="n">
+        <v>319.16</v>
+      </c>
+      <c r="J216" t="n">
+        <v>326.77</v>
+      </c>
+      <c r="K216" t="n">
+        <v>333.45</v>
+      </c>
+      <c r="L216" t="n">
+        <v>348.26</v>
+      </c>
+      <c r="M216" t="n">
+        <v>354.81</v>
+      </c>
+      <c r="N216" t="n">
+        <v>354.89</v>
+      </c>
+      <c r="O216" t="n">
+        <v>354.8</v>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>351.63</v>
+      </c>
+      <c r="C217" t="n">
+        <v>330.39</v>
+      </c>
+      <c r="D217" t="n">
+        <v>317.43</v>
+      </c>
+      <c r="E217" t="n">
+        <v>318.83</v>
+      </c>
+      <c r="F217" t="n">
+        <v>319.4</v>
+      </c>
+      <c r="G217" t="n">
+        <v>319.32</v>
+      </c>
+      <c r="H217" t="n">
+        <v>316.39</v>
+      </c>
+      <c r="I217" t="n">
+        <v>318.39</v>
+      </c>
+      <c r="J217" t="n">
+        <v>327.58</v>
+      </c>
+      <c r="K217" t="n">
+        <v>333.31</v>
+      </c>
+      <c r="L217" t="n">
+        <v>346.48</v>
+      </c>
+      <c r="M217" t="n">
+        <v>353.89</v>
+      </c>
+      <c r="N217" t="n">
+        <v>353.98</v>
+      </c>
+      <c r="O217" t="n">
+        <v>354.79</v>
+      </c>
+      <c r="P217" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -12080,7 +12188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B218"/>
+  <dimension ref="A1:B220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14263,6 +14371,26 @@
       </c>
       <c r="B218" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -14431,28 +14559,28 @@
         <v>0.06900000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2991207490516472</v>
+        <v>-0.3041764887717804</v>
       </c>
       <c r="J2" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K2" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08255389499764021</v>
+        <v>0.08669108758351229</v>
       </c>
       <c r="M2" t="n">
-        <v>6.278083383629184</v>
+        <v>6.248599402408542</v>
       </c>
       <c r="N2" t="n">
-        <v>61.47440577615614</v>
+        <v>60.98120412546402</v>
       </c>
       <c r="O2" t="n">
-        <v>7.840561572754603</v>
+        <v>7.809046300635182</v>
       </c>
       <c r="P2" t="n">
-        <v>362.8107967026659</v>
+        <v>362.8582856817243</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -14509,28 +14637,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.44149397097784</v>
+        <v>-0.4627255941327572</v>
       </c>
       <c r="J3" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K3" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08586762071980181</v>
+        <v>0.09445496776096474</v>
       </c>
       <c r="M3" t="n">
-        <v>8.985485458029412</v>
+        <v>9.01287553884355</v>
       </c>
       <c r="N3" t="n">
-        <v>128.2884284233705</v>
+        <v>128.4203231423713</v>
       </c>
       <c r="O3" t="n">
-        <v>11.32644818216949</v>
+        <v>11.33226910827533</v>
       </c>
       <c r="P3" t="n">
-        <v>354.1256758068856</v>
+        <v>354.3250924725364</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -14587,28 +14715,28 @@
         <v>0.1034</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3749751167459711</v>
+        <v>-0.3997025499295088</v>
       </c>
       <c r="J4" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K4" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05042991110296957</v>
+        <v>0.05745749673733269</v>
       </c>
       <c r="M4" t="n">
-        <v>10.44329655280883</v>
+        <v>10.4428111503773</v>
       </c>
       <c r="N4" t="n">
-        <v>163.6824017667057</v>
+        <v>163.9568428145303</v>
       </c>
       <c r="O4" t="n">
-        <v>12.79384233788683</v>
+        <v>12.80456335899551</v>
       </c>
       <c r="P4" t="n">
-        <v>341.563649087084</v>
+        <v>341.7959014096631</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -14665,28 +14793,28 @@
         <v>0.0706</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4659381537700765</v>
+        <v>-0.4819246241225842</v>
       </c>
       <c r="J5" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K5" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07093965629913312</v>
+        <v>0.07670254959118339</v>
       </c>
       <c r="M5" t="n">
-        <v>10.53409984314457</v>
+        <v>10.51483949572388</v>
       </c>
       <c r="N5" t="n">
-        <v>175.7800806550038</v>
+        <v>174.9006958973453</v>
       </c>
       <c r="O5" t="n">
-        <v>13.25820804841302</v>
+        <v>13.22500268042866</v>
       </c>
       <c r="P5" t="n">
-        <v>340.3924531007959</v>
+        <v>340.5426062447028</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -14743,28 +14871,28 @@
         <v>0.0582</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5797139367560338</v>
+        <v>-0.5887743953504865</v>
       </c>
       <c r="J6" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K6" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1021129640239617</v>
+        <v>0.1068689655167433</v>
       </c>
       <c r="M6" t="n">
-        <v>10.33319963727136</v>
+        <v>10.28936209015588</v>
       </c>
       <c r="N6" t="n">
-        <v>182.6949607794664</v>
+        <v>181.2436801370377</v>
       </c>
       <c r="O6" t="n">
-        <v>13.51646998219085</v>
+        <v>13.46267730197221</v>
       </c>
       <c r="P6" t="n">
-        <v>339.9094472622238</v>
+        <v>339.994547046713</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14821,28 +14949,28 @@
         <v>0.0497</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3970387622577638</v>
+        <v>-0.4076642979278836</v>
       </c>
       <c r="J7" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K7" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0520012898770551</v>
+        <v>0.05567154695487253</v>
       </c>
       <c r="M7" t="n">
-        <v>9.982749668494588</v>
+        <v>9.949179214256752</v>
       </c>
       <c r="N7" t="n">
-        <v>177.6714776185856</v>
+        <v>176.3585869527456</v>
       </c>
       <c r="O7" t="n">
-        <v>13.32934648130154</v>
+        <v>13.28000703888163</v>
       </c>
       <c r="P7" t="n">
-        <v>335.4989243700976</v>
+        <v>335.5987208083608</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14899,28 +15027,28 @@
         <v>0.051</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.424703713474155</v>
+        <v>-0.4345428317330401</v>
       </c>
       <c r="J8" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K8" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0490460980522498</v>
+        <v>0.05219921552369466</v>
       </c>
       <c r="M8" t="n">
-        <v>11.29872621803871</v>
+        <v>11.24575550590576</v>
       </c>
       <c r="N8" t="n">
-        <v>216.2147843709529</v>
+        <v>214.4962651303717</v>
       </c>
       <c r="O8" t="n">
-        <v>14.70424375379274</v>
+        <v>14.64569100897502</v>
       </c>
       <c r="P8" t="n">
-        <v>333.3591254356486</v>
+        <v>333.4515398572624</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -14977,28 +15105,28 @@
         <v>0.0674</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.306389450938162</v>
+        <v>-0.3139176074458103</v>
       </c>
       <c r="J9" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K9" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02887939948853002</v>
+        <v>0.03087357226080423</v>
       </c>
       <c r="M9" t="n">
-        <v>10.77287620327079</v>
+        <v>10.70753400274084</v>
       </c>
       <c r="N9" t="n">
-        <v>195.1600374542979</v>
+        <v>193.5202301846708</v>
       </c>
       <c r="O9" t="n">
-        <v>13.96996912860934</v>
+        <v>13.91115488321048</v>
       </c>
       <c r="P9" t="n">
-        <v>331.1959818554578</v>
+        <v>331.2666931341599</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -15055,28 +15183,28 @@
         <v>0.0619</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3637628218498085</v>
+        <v>-0.3657825734721484</v>
       </c>
       <c r="J10" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K10" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04592804231322989</v>
+        <v>0.04735705824496561</v>
       </c>
       <c r="M10" t="n">
-        <v>9.934714293069566</v>
+        <v>9.851181593791749</v>
       </c>
       <c r="N10" t="n">
-        <v>169.9409669652755</v>
+        <v>168.3809386167796</v>
       </c>
       <c r="O10" t="n">
-        <v>13.03614080030112</v>
+        <v>12.97616810220874</v>
       </c>
       <c r="P10" t="n">
-        <v>337.9730515899258</v>
+        <v>337.9920185487619</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -15133,28 +15261,28 @@
         <v>0.0475</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2383367593647405</v>
+        <v>-0.2446785710427404</v>
       </c>
       <c r="J11" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K11" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02138664914130628</v>
+        <v>0.02296743351192831</v>
       </c>
       <c r="M11" t="n">
-        <v>9.940155165369561</v>
+        <v>9.886253197983207</v>
       </c>
       <c r="N11" t="n">
-        <v>160.6973515400614</v>
+        <v>159.3271947737406</v>
       </c>
       <c r="O11" t="n">
-        <v>12.67664591049467</v>
+        <v>12.62248766185733</v>
       </c>
       <c r="P11" t="n">
-        <v>343.3185928441007</v>
+        <v>343.3781587517695</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -15211,28 +15339,28 @@
         <v>0.0616</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3507735242832324</v>
+        <v>-0.341377273672172</v>
       </c>
       <c r="J12" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K12" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04236911015876998</v>
+        <v>0.04098257708526576</v>
       </c>
       <c r="M12" t="n">
-        <v>10.85191552678685</v>
+        <v>10.78814776199338</v>
       </c>
       <c r="N12" t="n">
-        <v>171.9335709820392</v>
+        <v>170.6074182113767</v>
       </c>
       <c r="O12" t="n">
-        <v>13.11234422145938</v>
+        <v>13.06167746544741</v>
       </c>
       <c r="P12" t="n">
-        <v>351.3016110924009</v>
+        <v>351.2133646564394</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -15289,28 +15417,28 @@
         <v>0.0581</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2204300708743276</v>
+        <v>-0.2102298411117189</v>
       </c>
       <c r="J13" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K13" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01686907127945714</v>
+        <v>0.01566342722014324</v>
       </c>
       <c r="M13" t="n">
-        <v>10.32661293408101</v>
+        <v>10.27389244911534</v>
       </c>
       <c r="N13" t="n">
-        <v>175.0733869762375</v>
+        <v>173.7588841062248</v>
       </c>
       <c r="O13" t="n">
-        <v>13.23153003156617</v>
+        <v>13.18176331551378</v>
       </c>
       <c r="P13" t="n">
-        <v>354.3717802854837</v>
+        <v>354.2759787954078</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -15367,28 +15495,28 @@
         <v>0.0492</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3590451214423012</v>
+        <v>-0.3507783951021184</v>
       </c>
       <c r="J14" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K14" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03788984505193715</v>
+        <v>0.0369373811538084</v>
       </c>
       <c r="M14" t="n">
-        <v>11.3175799962157</v>
+        <v>11.24853242494636</v>
       </c>
       <c r="N14" t="n">
-        <v>202.3756687994528</v>
+        <v>200.7037862138875</v>
       </c>
       <c r="O14" t="n">
-        <v>14.22588024691101</v>
+        <v>14.16699637233974</v>
       </c>
       <c r="P14" t="n">
-        <v>359.2328208024514</v>
+        <v>359.1551796469381</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -15445,28 +15573,28 @@
         <v>0.0406</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.632083869487238</v>
+        <v>-0.6217906856308948</v>
       </c>
       <c r="J15" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K15" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09324518136688165</v>
+        <v>0.09215227310471208</v>
       </c>
       <c r="M15" t="n">
-        <v>12.57523361302438</v>
+        <v>12.50229758175612</v>
       </c>
       <c r="N15" t="n">
-        <v>240.1989787285861</v>
+        <v>238.2850792828496</v>
       </c>
       <c r="O15" t="n">
-        <v>15.49835406514466</v>
+        <v>15.43648532804179</v>
       </c>
       <c r="P15" t="n">
-        <v>365.6765471719963</v>
+        <v>365.579868720791</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -15504,7 +15632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P215"/>
+  <dimension ref="A1:P217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33137,6 +33265,170 @@
         </is>
       </c>
     </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>-34.45491408282109,173.00348440445032</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>-34.455650248354935,173.00322358933914</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>-34.45638828672993,173.00306628234165</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-34.45712909775731,173.00306201145082</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-34.45786968872943,173.00304598528035</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-34.458610039875985,173.00301711503218</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-34.459342726249496,173.00297687914045</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-34.460068951836526,173.00295542424604</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-34.460806068628635,173.00295875053834</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>-34.46154915239751,173.00295131749323</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>-34.46230122051787,173.0030317941032</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>-34.46304757822885,173.00305275534618</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>-34.463789540911925,173.0030331674593</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>-34.464529974922684,173.00301179166834</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:16:47+00:00</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>-34.454913938544315,173.00347645884665</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>-34.45565028393401,173.00322554854617</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>-34.456388259055416,173.00306475850056</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-34.45712906612935,173.00306026990282</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-34.45786970256671,173.00304674721434</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-34.458610203947934,173.003026149472</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-34.45934265938035,173.00297481207647</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-34.4600684486355,173.00294706277893</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-34.460806717086484,173.0029675348127</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-34.46154904031858,173.00294979921009</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>-34.46230006206857,173.0030124640634</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>-34.46304725382527,173.00304274599173</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>-34.463789354903135,173.00302326178328</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>-34.46452997287862,173.0030116828138</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
